--- a/Services/Fsel.Course/Fsel.Course.Lcms.Api/Resources/ExportExcelTemplates/BaoCao_Capso.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lcms.Api/Resources/ExportExcelTemplates/BaoCao_Capso.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\FSEL_All\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lcms.Api\Resources\ExportExcelTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lcms.Api\Resources\ExportExcelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70619567-C48D-405F-BC6C-48F6FD29F12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t>BÁO CÁO GIAI ĐOẠN ĐĂNG KÝ "THÁNG TỰ HỌC TIẾNG ANH"</t>
   </si>
@@ -83,17 +84,130 @@
   </si>
   <si>
     <t>THCS</t>
+  </si>
+  <si>
+    <t>BÁO CÁO XÁC THỰC</t>
+  </si>
+  <si>
+    <t>BÁO CÁO ĐÁNH GIÁ ĐẦU VÀO (PT)</t>
+  </si>
+  <si>
+    <t>BÁO CÁO VÀO HỌC</t>
+  </si>
+  <si>
+    <t>Số HS xác thực thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỷ lệ HS xác thực thành công/SL thực tế </t>
+  </si>
+  <si>
+    <t>Số lượng GV xác thực thành công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tỷ lệ GV xác thực thành công/ SL thực tế </t>
+  </si>
+  <si>
+    <t>Tổng số Học viên xác thực thành công
+(HS+GV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỷ lệ học viên xác thực tham gia/SL thực tế </t>
+  </si>
+  <si>
+    <t>HỌC SINH</t>
+  </si>
+  <si>
+    <t>GIÁO VIÊN</t>
+  </si>
+  <si>
+    <t>HỌC VIÊN</t>
+  </si>
+  <si>
+    <t>Số HS đã học trên hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỷ lệ HS đã học/SL thực tế </t>
+  </si>
+  <si>
+    <t>Số GV đã học trên hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỷ lệ GV đã học/SL thực tế </t>
+  </si>
+  <si>
+    <t>Số Học viên (HS+GV) đã học trên hệ thống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỷ lệ học viên đã học/SL thực tế </t>
+  </si>
+  <si>
+    <t>Tổng số Học viên xác thực
+(HS+GV)</t>
+  </si>
+  <si>
+    <t>SL HS đã hoàn thành PT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HS hoàn thành PT/SL đăng ký</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HS hoàn thành PT/SL thực tế</t>
+  </si>
+  <si>
+    <t>SL HS đang PT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HS đang PT/SL đăng ký</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HS đang PT/SL thực tế</t>
+  </si>
+  <si>
+    <t>SL GV đã hoàn thành PT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ GV hoàn thành PT/SL đăng ký</t>
+  </si>
+  <si>
+    <t>Tỷ lệ GV hoàn thành PT/SL thực tế</t>
+  </si>
+  <si>
+    <t>SL GV đang PT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ GV đang PT/SL đăng ký</t>
+  </si>
+  <si>
+    <t>Tỷ lệ GV đang PT/SL thực tế</t>
+  </si>
+  <si>
+    <t>SL HV đã hoàn thành PT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HV hoàn thành PT/SL đăng ký</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HV hoàn thành PT/SL thực tế</t>
+  </si>
+  <si>
+    <t>SL HV đang PT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HV đang PT/SL đăng ký</t>
+  </si>
+  <si>
+    <t>Tỷ lệ HV đang PT/SL thực tế</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -101,7 +215,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -109,7 +223,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -117,7 +231,7 @@
       <b/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -125,7 +239,7 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -133,19 +247,19 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,8 +284,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -207,11 +333,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -229,32 +366,43 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -570,18 +718,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultColWidth="18.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AR9"/>
+  <sheetFormatPr defaultColWidth="18.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" style="2" customWidth="1"/>
-    <col min="3" max="6" width="18.28515625" style="2" customWidth="1"/>
-    <col min="7" max="14" width="20.85546875" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="18.7109375" style="2"/>
+    <col min="1" max="1" width="15.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.625" style="2" customWidth="1"/>
+    <col min="3" max="6" width="18.25" style="2" customWidth="1"/>
+    <col min="7" max="14" width="20.875" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="18.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:44" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +737,7 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:18" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:44" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -597,7 +745,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:18" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:44" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -605,135 +753,340 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:18" s="5" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:44" s="5" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="18"/>
+      <c r="AM4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN4" s="19"/>
+      <c r="AO4" s="19"/>
+      <c r="AP4" s="19"/>
+      <c r="AQ4" s="19"/>
+      <c r="AR4" s="19"/>
     </row>
-    <row r="5" spans="1:18" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:44" s="6" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="12" t="s">
         <v>16</v>
       </c>
+      <c r="O5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="17"/>
+      <c r="AG5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH5" s="17"/>
+      <c r="AI5" s="17"/>
+      <c r="AJ5" s="17"/>
+      <c r="AK5" s="17"/>
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR5" s="11" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:44" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="V6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH6" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI6" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AR6" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
     </row>
-    <row r="7" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8"/>
     </row>
-    <row r="8" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A9"/>
     </row>
-    <row r="9" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-    </row>
-    <row r="10" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-    </row>
-    <row r="11" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="20" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="21" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="22" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="23" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="34">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="U5:Z5"/>
+    <mergeCell ref="AA5:AF5"/>
+    <mergeCell ref="AG5:AL5"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:N4"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="U4:AL4"/>
+    <mergeCell ref="AM4:AR4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2AA525DA2F333468273E03D890440D6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a0f9360bda923dd7fb76d00a461df4cd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9c5e610e-28db-44df-ba41-c446aaffe434" xmlns:ns4="e78f2374-cb69-45b5-92b0-6a1f828922e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e929c21602ddc082d402d6da66c8cbef" ns3:_="" ns4:_="">
     <xsd:import namespace="9c5e610e-28db-44df-ba41-c446aaffe434"/>
@@ -960,24 +1313,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86991C2-FEE0-4077-9DDC-1AA02DDC74D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8C5EC61-FAED-44C4-88DF-892B92051A1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FD517CC-29C0-4CF0-A3AE-62F8C514AAA9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -994,29 +1355,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8C5EC61-FAED-44C4-88DF-892B92051A1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86991C2-FEE0-4077-9DDC-1AA02DDC74D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Services/Fsel.Course/Fsel.Course.Lcms.Api/Resources/ExportExcelTemplates/BaoCao_Capso.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lcms.Api/Resources/ExportExcelTemplates/BaoCao_Capso.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lcms.Api\Resources\ExportExcelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70619567-C48D-405F-BC6C-48F6FD29F12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7E0AC2-838A-455A-ADF1-59E4ED5A15AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
-    <t>BÁO CÁO GIAI ĐOẠN ĐĂNG KÝ "THÁNG TỰ HỌC TIẾNG ANH"</t>
-  </si>
-  <si>
     <t>Cấp : Sở GDĐT</t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>Tỷ lệ HV đang PT/SL thực tế</t>
+  </si>
+  <si>
+    <t>BÁO CÁO HỌC TẬP "THÁNG TỰ HỌC TIẾNG ANH"</t>
   </si>
 </sst>
 </file>
@@ -369,21 +369,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -391,12 +397,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -731,7 +731,7 @@
   <sheetData>
     <row r="1" spans="1:44" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -739,7 +739,7 @@
     </row>
     <row r="2" spans="1:44" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -747,61 +747,61 @@
     </row>
     <row r="3" spans="1:44" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:44" s="5" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="13" t="s">
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="15"/>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="15"/>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="15"/>
-      <c r="AE4" s="15"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="15"/>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="15"/>
-      <c r="AK4" s="15"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="17"/>
+      <c r="AI4" s="17"/>
+      <c r="AJ4" s="17"/>
+      <c r="AK4" s="17"/>
       <c r="AL4" s="18"/>
       <c r="AM4" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN4" s="19"/>
       <c r="AO4" s="19"/>
@@ -810,216 +810,216 @@
       <c r="AR4" s="19"/>
     </row>
     <row r="5" spans="1:44" s="6" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="12" t="s">
-        <v>17</v>
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="L5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="M5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="O5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="Q5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="R5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="S5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="11" t="s">
+      <c r="T5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="T5" s="11" t="s">
+      <c r="U5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="U5" s="17" t="s">
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17" t="s">
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="17" t="s">
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="17"/>
-      <c r="AL5" s="17"/>
-      <c r="AM5" s="11" t="s">
+      <c r="AN5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AN5" s="11" t="s">
+      <c r="AO5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AO5" s="11" t="s">
+      <c r="AP5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AP5" s="11" t="s">
+      <c r="AQ5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="AQ5" s="11" t="s">
+      <c r="AR5" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="AR5" s="11" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:44" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="16"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="11"/>
-      <c r="N6" s="12"/>
+      <c r="N6" s="10"/>
       <c r="O6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="Q6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="R6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R6" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="S6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="U6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="T6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="U6" s="10" t="s">
+      <c r="V6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="V6" s="10" t="s">
+      <c r="W6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="W6" s="10" t="s">
+      <c r="X6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="X6" s="10" t="s">
+      <c r="Y6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Z6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Z6" s="10" t="s">
+      <c r="AA6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="AA6" s="10" t="s">
+      <c r="AB6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="AB6" s="10" t="s">
+      <c r="AC6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AC6" s="10" t="s">
+      <c r="AD6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AD6" s="10" t="s">
+      <c r="AE6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AE6" s="10" t="s">
+      <c r="AF6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AF6" s="10" t="s">
+      <c r="AG6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AG6" s="10" t="s">
+      <c r="AH6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AH6" s="10" t="s">
+      <c r="AI6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="AI6" s="10" t="s">
+      <c r="AJ6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="AJ6" s="10" t="s">
+      <c r="AK6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AL6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="AL6" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="AM6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="AN6" s="11" t="s">
-        <v>23</v>
-      </c>
       <c r="AO6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="11" t="s">
-        <v>23</v>
-      </c>
       <c r="AQ6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR6" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="AR6" s="11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:44" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
@@ -1030,20 +1030,16 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:N4"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="U4:AL4"/>
+    <mergeCell ref="AM4:AR4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="AP5:AP6"/>
     <mergeCell ref="AQ5:AQ6"/>
@@ -1054,39 +1050,26 @@
     <mergeCell ref="AM5:AM6"/>
     <mergeCell ref="AN5:AN6"/>
     <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:N4"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="U4:AL4"/>
-    <mergeCell ref="AM4:AR4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="J5:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2AA525DA2F333468273E03D890440D6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a0f9360bda923dd7fb76d00a461df4cd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9c5e610e-28db-44df-ba41-c446aaffe434" xmlns:ns4="e78f2374-cb69-45b5-92b0-6a1f828922e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e929c21602ddc082d402d6da66c8cbef" ns3:_="" ns4:_="">
     <xsd:import namespace="9c5e610e-28db-44df-ba41-c446aaffe434"/>
@@ -1313,32 +1296,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86991C2-FEE0-4077-9DDC-1AA02DDC74D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8C5EC61-FAED-44C4-88DF-892B92051A1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9c5e610e-28db-44df-ba41-c446aaffe434" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FD517CC-29C0-4CF0-A3AE-62F8C514AAA9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1355,4 +1330,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8C5EC61-FAED-44C4-88DF-892B92051A1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86991C2-FEE0-4077-9DDC-1AA02DDC74D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="e78f2374-cb69-45b5-92b0-6a1f828922e7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9c5e610e-28db-44df-ba41-c446aaffe434"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>